--- a/Result/profitability/3030.xlsx
+++ b/Result/profitability/3030.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.37</v>
       </c>
       <c r="M2" t="n">
-        <v>2.27875</v>
+        <v>2.55625</v>
       </c>
       <c r="N2" t="n">
-        <v>58.925</v>
+        <v>58.86625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.47</v>
       </c>
       <c r="M3" t="n">
-        <v>2.2575</v>
+        <v>2.46125</v>
       </c>
       <c r="N3" t="n">
-        <v>58.195</v>
+        <v>57.8425</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.03</v>
       </c>
       <c r="M4" t="n">
-        <v>2.1075</v>
+        <v>2.28375</v>
       </c>
       <c r="N4" t="n">
-        <v>57.45625</v>
+        <v>57.5925</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.02</v>
       </c>
       <c r="M5" t="n">
-        <v>1.79875</v>
+        <v>2.005</v>
       </c>
       <c r="N5" t="n">
-        <v>56.5725</v>
+        <v>56.6125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.12</v>
       </c>
       <c r="M6" t="n">
-        <v>1.5075</v>
+        <v>1.62375</v>
       </c>
       <c r="N6" t="n">
-        <v>55.4725</v>
+        <v>55.72125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.23</v>
       </c>
       <c r="M7" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="N7" t="n">
-        <v>54.90625</v>
+        <v>54.66375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.45</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8637499999999999</v>
+        <v>0.9087499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>54.09375</v>
+        <v>53.8975</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3030</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2947</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1217</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1730</v>
+      </c>
+      <c r="F75" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1148</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>38.95%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1144</v>
+      </c>
+      <c r="K75" t="n">
+        <v>912</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.715</v>
+      </c>
+      <c r="N75" t="n">
+        <v>59.125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.3599999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1028571428571428</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.02604944416791111</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.746606334841629</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.3200000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.005481329222336351</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
